--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_012/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_012/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -434,6 +439,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -505,11 +515,6 @@
       </text>
     </comment>
     <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1311,12 +1316,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Conjugate heat transfer prediction of 120 W processor module die temperature and pressure drop for thermal margin assessment</t>
+          <t>Conjugate heat transfer prediction of 120 W processor module with dual 40 mm blowers</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Steady-state conjugate thermal-fluid model of a 120 W avionics processor module with dual 40 mm radial blowers, pin-fin heat sink, PCB stackup, and TIM2 interface. Model predicts die temperature, baseplate temperature, and module pressure drop across ambient 20–50 C and sea level to 5 km altitude. Results used to assess thermal design margins prior to Rev C hardware freeze.</t>
+          <t>Steady-state RANS CHT simulation predicting die and baseplate temperatures, module pressure drop, and outlet bulk temperature rise for a 120 W avionics processor module cooled by dual 40 mm radial blowers. The model is used to assess thermal margin against component temperature limits across an ambient range of 20–50 C and altitudes up to 5 km.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1354,9 +1359,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1475,7 +1480,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Thermal Margin Requirement — Die Temperature and Pressure Drop</t>
+          <t>Thermal Margin Requirement</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1485,7 +1490,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>The CHT model must predict die centerline temperature and module pressure drop within acceptable error bounds relative to bench measurements to support Rev C design margin assessment; design margin must absorb at least +5 C headroom at 100 W.</t>
+          <t>Die and baseplate temperatures must remain within component rated limits across the full operating envelope (20–50 C ambient, sea level to 5 km altitude, 100–120 W input power), with model-to-measurement agreement adequate to confirm sufficient design margin.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1507,12 +1512,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>CHT Model — Ansys Fluent 2023 R1 (Rev C, avx-cht-revC-2026-07-29)</t>
+          <t>CHT RANS Model — Avionics Processor Module</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Steady RANS (k-omega SST) conjugate heat transfer model of the 120 W processor module including heat sink, housing, PCB stackup, die/lid/TIM2, and dual 40 mm blowers; 9.8M-cell poly-hybrid fine mesh.</t>
+          <t>Steady RANS k-omega SST conjugate thermal-fluid model in Ansys Fluent 2023 R1 covering heat sink, PCB stackup, die/lid/TIM2, housing, and dual blowers with surface-to-surface radiation and temperature-dependent material properties.</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1529,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Rev B Bench Measurements — 100 W Heater Block Validation</t>
+          <t>Rev B Bench Rig Validation Dataset</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Laboratory measurements using a copper heater block stand-in at 100.0 W ±0.5%; 8 K-type thermocouples on baseplate and lid, pitot rake at outlet, ambient 24.3 ±0.2 C; provides reference temperatures and pressure drop for model comparison.</t>
+          <t>Lab measurements from copper heater block stand-in at 100 W: 8 K-type thermocouple readings on lid and baseplate, pitot rake outlet flow, module differential pressure (142 ±7 Pa), ambient 24.3 ±0.2 C.</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1551,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Thermal conductivity k(T) from ASM Digital Library for 6061-T6, copper lid, and FR-4 effective values; TIM2 1.5 W/m-K (Parker Chomerics); Delta BFB0412 fan curve digitized from datasheet (R^2=0.998); contact conductance from Mikic correlation at 1.2 N·m bolt torque.</t>
+          <t>Temperature-dependent thermal conductivities from ASM Digital Library for 6061-T6, copper lid, and FR-4 effective k; TIM2 conductivity 1.5 W/m-K (Parker Chomerics); Delta BFB0412 fan curve digitized from datasheet (R²=0.998) with ambient density correction.</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1988,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Die Lid Temperature Comparison — 100 W Bench Case</t>
+          <t>Lid Centerline Temperature Comparison</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1998,12 +2003,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Model-predicted lid centerline temperature compared to K-type thermocouple measurement at 100 W input power, ambient 24.3 C.</t>
+          <t>Model-predicted lid centerline temperature compared to K-type thermocouple measurement at 100 W input power</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Measured lid centerline temperature 78.2 C (Rev B bench hardware)</t>
+          <t>Measured 78.2 C (Rev B bench rig, K-type thermocouple)</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2013,12 +2018,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Measurement uncertainty on power (±0.5%), ambient temperature (±0.2 C); sensitivity sweeps on contact conductance, emissivity, fan curve, and total power</t>
+          <t>Thermocouple measurements with controlled ambient ±0.2 C; power supply ±0.5%</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>+0.9 C absolute error (1.1% relative); within sensitivity band</t>
+          <t>+0.9 C absolute error (1.1% relative)</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2030,7 +2035,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Baseplate Temperature Comparison — Screw Boss Location</t>
+          <t>Baseplate Temperature Comparison</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2040,22 +2045,27 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Model-predicted baseplate temperature near screw boss compared to thermocouple measurement.</t>
+          <t>Model-predicted baseplate temperature near screw boss compared to thermocouple measurement at 100 W</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Measured baseplate temperature 63.5 C (Rev B bench hardware)</t>
+          <t>Measured 63.5 C (Rev B bench rig, K-type thermocouple)</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Same thermocouple instrumentation as lid measurement</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>-0.9 C absolute error (1.4% relative)</t>
+          <t>-0.9 C absolute error</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2067,7 +2077,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Module Pressure Drop Comparison</t>
+          <t>Module Differential Pressure Comparison</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2077,12 +2087,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Predicted module differential pressure compared to pitot rake measurement at nominal 100 W operating condition.</t>
+          <t>Model-predicted module pressure drop compared to pitot rake measurement at 100 W</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Measured module Δp 142 ±7 Pa (pitot rake, Rev B bench)</t>
+          <t>Measured 142 ±7 Pa (pitot rake)</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2092,12 +2102,12 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Measurement uncertainty ±7 Pa reported; fan curve sensitivity ±10% explored</t>
+          <t>Pitot rake measurement uncertainty ±7 Pa</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Model 135 Pa vs. 142 Pa measured; -4.9% error; within measurement uncertainty band (±4.9%)</t>
+          <t>-4.9% (model 135 Pa vs. measured 142 Pa); within measurement uncertainty band</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2109,7 +2119,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study</t>
+          <t>Mesh Refinement / Convergence Study</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2119,27 +2129,22 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement study (2.1M coarse, 4.5M medium, 9.8M fine cells) assessing discretization error on maximum die temperature.</t>
+          <t>Three-level mesh refinement study: coarse 2.1M, medium 4.5M, fine 9.8M cells; change in max die temperature assessed between levels</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / GCI not explicitly computed; level-to-level differences reported</t>
+          <t>Richardson extrapolation criterion (monotone convergence); fine grid selected for production</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Level-to-level temperature difference reported; fine mesh selected based on convergence trend</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Medium-to-fine change: 1.8 C (2.2%); coarse-to-medium change: 3.9 C (4.7%); monotone convergence trend</t>
+          <t>Medium-to-fine change: 1.8 C (2.2%); coarse-to-medium: 3.9 C (4.7%)</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2151,7 +2156,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Independent Model Recreation Check</t>
+          <t>Independent Model Reproducibility Check</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2161,12 +2166,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Independent analyst J. Park recreated the medium mesh from the setup checklist and re-ran the 100 W case to verify reproducibility and use correctness.</t>
+          <t>Independent analyst J. Park recreated medium mesh from checklist and ran 100 W case independently</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Original analyst results: T_die and Δp from primary run</t>
+          <t>Primary analyst results (T_die and delta-p)</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2176,7 +2181,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>T_die agreement within 0.3 C; Δp agreement within 6 Pa</t>
+          <t>T_die agreement within 0.3 C; delta-p agreement within 6 Pa</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2330,12 +2335,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Evidence of commercial solver with version control and reproducible run environment</t>
+          <t>Simulation software documented, versioned, and reproducible on independent hardware</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023 R1 and ICEM 2022 R2 are commercial, widely validated solvers. Case files and scripts are under GitLab version control (tag avx-cht-revC-2026-07-29, commit 0f3c9c2) with README documenting run steps and machine file. Runs reproduced on two independent hardware platforms (JSC Merope and local workstation) with T_die agreement within 0.2 C. No explicit ISO quality certification or regression test suite described beyond version-controlled case tree.</t>
+          <t>Ansys Fluent 2023 R1 and ICEM 2022 R2 are commercial solvers with documented QA practices. Case and scripts are under GitLab version control (tag avx-cht-revC-2026-07-29, commit 0f3c9c2) with a README including run steps. Runs reproduced on two independent hardware platforms (JSC Merope 32-core AMD EPYC and local 16-core workstation) with T_die agreement within 0.2 C. No explicit ISO certification or formal regression test suite documented.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2364,12 +2369,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Evidence that the solver correctly implements governing equations for CHT and RANS turbulence</t>
+          <t>Evidence that code correctly solves governing equations for relevant physics</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Ansys Fluent is a commercially verified solver with documented governing equations for RANS and conjugate heat transfer; no project-specific MMS or benchmark comparison to analytical solutions is reported in this document. Reliance on commercial solver reputation provides basic but not independently confirmed code verification for this application.</t>
+          <t>Ansys Fluent is a widely used commercial solver with established k-omega SST and CHT implementations. No specific MMS or analytical solution comparison is reported for this study. Reliance is on the commercial solver's established verification heritage. No benchmark problem results are cited explicitly in the document.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2398,12 +2403,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence study demonstrating adequate spatial resolution for QoI</t>
+          <t>Mesh convergence demonstrated with quantified change in QoI between refinement levels</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement study performed (2.1M, 4.5M, 9.8M cells). Monotone convergence observed: coarse-to-medium change 3.9 C (4.7%), medium-to-fine change 1.8 C (2.2%), indicating convergence trend. Fine mesh adopted for production runs. GCI or Richardson extrapolation not explicitly computed, which limits achievement of level 4. Near-wall y+ 30–60 with wall functions documented.</t>
+          <t>Three-level mesh refinement study performed: coarse 2.1M, medium 4.5M, fine 9.8M cells. Max die temperature change from medium to fine: 1.8 C (2.2%); coarse to medium: 3.9 C (4.7%). Fine grid adopted for production. Near-wall y+ 30–60 with wall functions on heat-sink pins. GCI or Richardson extrapolation not explicitly computed, limiting achievement to level 3.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2432,12 +2437,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residuals and global quantities demonstrating iterative convergence</t>
+          <t>Residual convergence and solution monitors demonstrate fully converged solution</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Residuals reported below 1e-5 (energy) and 5e-4 (flow). Global monitors (heat rate and pressure drop) confirmed flat over the last 500 iterations. Interface heat-balance mismatch under 0.3% at solver stop. URFs documented (energy 0.9, momentum 0.7). Convergence criteria are explicit and monitored with multiple indicators.</t>
+          <t>Residual targets documented: energy below 1e-5, flow below 5e-4. Heat rate and pressure drop flat over last 500 iterations. Interface heat-balance mismatch under 0.3%. Segregated CHT with 10 outer loops per solve; URFs documented (energy 0.9, momentum 0.7). Quantitative convergence evidence is present and adequate.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2466,12 +2471,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent review or recreation confirming correct model setup and boundary conditions</t>
+          <t>Independent review of model setup; boundary conditions and mesh quality verified</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Independent analyst J. Park recreated the medium mesh from the setup checklist and matched the 100 W case within 0.3 C on T_die and 6 Pa on Δp, providing strong evidence of correct setup. GitLab version control with README run instructions supports repeatability. Boundary conditions (fan curve, power input, ambient) are explicitly documented. No formal checklist or independent boundary condition audit document cited beyond the recreation exercise.</t>
+          <t>Independent analyst J. Park recreated the medium mesh from a checklist and matched T_die within 0.3 C and delta-p within 6 Pa, providing strong evidence of correct setup. GitLab version control with documented README supports reproducibility. Fan curve boundary condition validated against datasheet (R²=0.998). Mesh quality parameters (y+, prism layers) documented. No formal sign-off checklist document cited, slightly limiting to level 4.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2500,12 +2505,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and turbulence model selection justified for the physics regime</t>
+          <t>Governing equation choices justified and known model limitations documented</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Steady RANS with k-omega SST selected; regime documented as pin-fin Re 2.2e4–3.8e4 (turbulent, within SST intended range). Conjugate conduction with temperature-dependent k(T) applied. Surface-to-surface radiation with precomputed view factors included and radiation confirmed active in both model and test chamber. Fan modeled as pressure-jump using manufacturer curve with density correction. Known simplifications (no cable harnesses) noted. Formal turbulence model selection study or comparison of alternative closures not reported.</t>
+          <t>Steady RANS k-omega SST selected for internal forced convection in pin-fin geometry; airside Reynolds numbers 2.2e4–3.8e4 cited as within intended regime. Conjugate conduction with temperature-dependent k(T), surface-to-surface radiation with precomputed view factors, and fan pressure-jump boundary condition are all documented with rationale. Operating range of applicability stated (30–90 C component temperature, 20–50 C ambient, sea level to 5 km). Power map uncertainty acknowledged as a remaining risk. No formal turbulence model selection study or comparison of alternative closures reported.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2534,12 +2539,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties, boundary conditions, and geometry inputs characterized with uncertainty</t>
+          <t>Material properties, boundary conditions, and geometry inputs traceable to measurements or qualified sources</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Material k(T) sourced from ASM Digital Library for all solids; FR-4 effective k fitted from IPC-2152. TIM2 conductivity from manufacturer datasheet (Parker Chomerics, 1.5 W/m-K). Contact conductance derived from Mikic correlation at documented bolt torque (1.2 N·m). Fan curve digitized with R^2=0.998 and density-corrected. Power map based on FPGA team estimate (acknowledged uncertainty; updated map identified as open action). Input uncertainty not formally propagated but sensitivity sweeps cover key uncertain inputs.</t>
+          <t>Material k(T) from ASM Digital Library for 6061-T6, copper, and FR-4 effective conductivity fitted from IPC-2152. TIM2 thermal conductivity 1.5 W/m-K from Parker Chomerics datasheet. Contact conductance 8,000 W/m²K derived from Mikic correlation at 1.2 N·m bolt torque. Fan curve digitized from manufacturer datasheet (R²=0.998) with density correction. Power map based on FPGA team estimate (70%/30% split) — acknowledged as uncertain. Sensitivity sweeps quantify input uncertainty impact on T_die. No direct measurement of contact conductance or die power distribution; these remain the dominant input uncertainties.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2568,12 +2573,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article described with adequate characterization for comparison</t>
+          <t>Test articles representative of production hardware with adequate characterization</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A single copper heater block stand-in (sized to die lid) used as the test article rather than production die hardware. Only one test article described; no statistical characterization across multiple specimens. Rev B hardware noted as distinction from Rev C target. This limits sample representativeness but is appropriate for a development-phase bench rig.</t>
+          <t>Validation used a single Rev B hardware configuration with a copper heater block stand-in (not the actual die). The heater block is described as the same size as the die lid but is not production hardware. Only one test article is referenced; no statistical characterization across multiple samples. Limited to level 2 due to single non-production surrogate specimen.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2602,12 +2607,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation and documented measurement uncertainty for temperature, power, and pressure</t>
+          <t>Controlled, well-instrumented test conditions with documented measurement uncertainty</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Power input 100.0 W ±0.5% DC. Ambient temperature 24.3 ±0.2 C. Eight K-type thermocouples on baseplate and lid. Pitot rake at outlet for pressure/flow. Radiation environment described (painted interior, ε ~0.8). Measurement uncertainties reported for power, ambient, and pressure drop (±7 Pa). Thermocouple calibration traceability and ASTM/ISO test standard adherence not explicitly stated, limiting achievement of level 4.</t>
+          <t>Power input 100.0 W ±0.5% DC, ambient 24.3 ±0.2 C documented. Eight K-type thermocouples on baseplate and lid. Pitot rake at outlet for flow measurement. Module delta-p 142 ±7 Pa with uncertainty stated. Radiation condition replicated (painted interior, ε ~0.8, low-speed airflow). No explicit instrument calibration certificates or test standard (ASTM/ISO) referenced; measurement uncertainty is stated but traceability is not documented in detail.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2636,12 +2641,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model boundary conditions matched to measured test conditions with uncertainty comparison</t>
+          <t>Model boundary conditions demonstrably match experimental test conditions</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Model run at same nominal power (100 W), ambient (24.3 C), and geometry as bench test. Fan curve ambient density correction applied to match test temperature. Radiation modeled with same estimated emissivity as chamber. Contact conductance and power map are acknowledged sources of mismatch between test and model inputs. Outlet bulk temperature rise matched within 0.3 C, providing a global energy balance check. Formal uncertainty propagation from test inputs to model inputs not documented.</t>
+          <t>Ambient temperature, input power, fan curve, radiation emissivity, and geometry are all matched between model and test. Radiation enabled in both model and chamber. Ambient density correction applied to fan curve. Outlet bulk temperature rise matches within 0.3 C, providing integral check of energy balance equivalency. Power map in the model uses heater block uniform input consistent with the copper heater stand-in. No formal uncertainty propagation from measurement to model inputs performed.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2670,12 +2675,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to measurements at multiple locations with error metrics</t>
+          <t>Quantitative comparison of model predictions to experimental measurements at multiple points with uncertainty bounds</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Lid centerline temperature: +0.9 C (1.1% error). Baseplate near screw boss: -0.9 C. Module Δp: -4.9% (135 vs. 142 Pa, within ±7 Pa measurement uncertainty). Outlet bulk temperature rise: within 0.3 C. Four distinct output quantities compared. Sensitivity sweeps provide context for uncertainty bands around predictions. Formal statistical validation metrics (e.g., Theil U, validation uncertainty interval) not computed; comparison is deterministic point-to-point.</t>
+          <t>Lid centerline temperature: +0.9 C (1.1%) error. Baseplate temperature: -0.9 C error. Module delta-p: -4.9% (135 vs. 142 ±7 Pa, within measurement uncertainty). Outlet bulk temperature rise matches within 0.3 C. Multiple spatial measurement points (8 thermocouples) and multiple quantities of interest (temperature, pressure, flow) compared. Measurement uncertainty on delta-p explicitly stated. No formal statistical validation metric (e.g., ASME V&amp;V 20 U95 band comparison) applied; scalar point comparisons only.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2704,12 +2709,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Model QoIs directly measure the thermal margin concern and are measurable both computationally and experimentally</t>
+          <t>Model QoIs directly correspond to the safety/performance concern and are measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Die temperature and module pressure drop are the primary thermal design margin QoIs. Both are predicted by the model and measured in the bench test. Temperature predictions at the die lid directly address the junction temperature margin concern. Pressure drop captures fan-module aerodynamic matching. Outlet bulk temperature confirms global energy balance. QoIs are directly traceable to the design requirement (5 C headroom at 100 W). Strong alignment between computational and experimental observables.</t>
+          <t>Primary QoIs are die temperature, baseplate temperature, and module pressure drop — directly corresponding to the thermal margin requirement and fan operating point assessment. All QoIs are measured in both experiment and model. Sensitivity sweeps provide additional insight into which QoIs drive design margin. Outlet bulk temperature rise provides an integral energy-balance QoI. QoIs are directly actionable for the design freeze decision.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2738,12 +2743,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions span the intended operating envelope (20–50 C ambient, sea level to 5 km, 100–120 W)</t>
+          <t>Validation conditions cover the full intended operating envelope including worst-case combinations</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation performed at a single operating point: 100 W, 24.3 C ambient, sea level. COU envelope extends to 120 W, 50 C ambient, and 5 km altitude. Fan density correction for elevated temperature and altitude is implemented but not bench-validated at those conditions. Power map representative of production FPGA not yet confirmed. Rev B heater block stand-in differs from Rev C production die. The single-point validation leaves the upper envelope (elevated temperature, altitude, and full power) without experimental confirmation, representing a meaningful gap relative to the full COU.</t>
+          <t>Validation performed at a single operating point: 100 W, 24.3 C ambient, sea level, with a heater block stand-in. The COU envelope extends to 120 W, 50 C ambient, and 5 km altitude. Fan curve temperature correction is modeled but not bench-validated at elevated temperature. Power map uncertainty (FPGA hotspot distribution) is unresolved. Rev B hardware used rather than final Rev C configuration. These gaps — particularly the unvalidated elevated-temperature/altitude regime and non-production test article — limit relevance to level 2. Sensitivity sweeps partially compensate but do not substitute for direct validation at envelope extremes.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2928,7 +2933,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The CHT model demonstrates agreement with bench measurements within 1.1% on die temperature and within measurement uncertainty on pressure drop across four comparison points. Mesh convergence, solver convergence, independent recreation, and sensitivity studies collectively provide adequate evidence for the current design-margin assessment at the 100 W nominal condition. Acceptance is granted with the following conditions to be resolved before Rev C freeze: (1) update the power map with the FPGA team's confirmed hotspot distribution; (2) lock in a conservative contact conductance lower bound in the design specification to protect the +5 C margin; (3) if schedule permits, validate fan curve at 45–50 C inlet on the bench to reduce altitude/temperature extrapolation risk. The model is accepted for thermal margin assessment at nominal conditions; extrapolation to the full 120 W / 50 C / 5 km envelope carries residual uncertainty acknowledged in the relevance-of-validation-activities factor.</t>
+          <t>The CHT model demonstrates agreement with bench measurements within 1.1% on lid temperature, within 0.9 C on baseplate temperature, and within measurement uncertainty on module pressure drop (-4.9% vs. ±4.9% measurement band). Independent reproducibility check passed. Mesh convergence is demonstrated with 2.2% change from medium to fine grid. The model is accepted for use in assessing thermal margin at the validated 100 W, sea-level, 24.3 C condition. Acceptance carries the following conditions: (1) contact conductance must be locked to a conservative specification band (≥8,000 W/m²K) or the +5 C sensitivity absorbed in design margin; (2) the FPGA power map must be confirmed and updated before final Rev C freeze; (3) fan curve validation at 45–50 C inlet temperature is recommended before extending model use to the full 50 C / 5 km altitude envelope; (4) model applicability beyond the validated single operating point should be treated with caution until additional envelope points are bench-confirmed.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
